--- a/doc/進捗.xlsx
+++ b/doc/進捗.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kirit\source\repos\DirectX12_3D-Refactoring\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD10218-7C2A-47C5-B6ED-E1A572CA55F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0445B83-0C71-4C60-A358-BB271C7F73DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{12C236FB-4823-4D4D-8EAA-B1916036AF64}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>タスク名</t>
     <rPh sb="3" eb="4">
@@ -172,6 +172,9 @@
   <si>
     <t>VFX</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
   </si>
 </sst>
 </file>
@@ -269,7 +272,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -288,35 +291,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color theme="2" tint="-0.499984740745262"/>
@@ -352,20 +327,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="3" tint="0.89996032593768116"/>
         </patternFill>
       </fill>
@@ -380,55 +341,16 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -837,29 +759,35 @@
         <v>13</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="B3" s="7">
+        <v>46087</v>
+      </c>
       <c r="C3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
+      <c r="B4" s="7">
+        <v>46086</v>
+      </c>
       <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -889,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="7">
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>15</v>
@@ -903,7 +831,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="7">
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>15</v>
@@ -1004,6 +932,9 @@
       <c r="A17" s="6" t="s">
         <v>26</v>
       </c>
+      <c r="C17" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="D17" s="8" t="s">
         <v>5</v>
       </c>
@@ -1020,35 +951,35 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>"重要"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"やや重要"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"普通"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"低い"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"進行中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"完了"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"完了"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="9" operator="equal">
       <formula>",完了"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"重要"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"やや重要"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"普通"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>"低い"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
